--- a/reports/빅딜/history/2026-06-10/빅딜_training_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-06-10/빅딜_training_mgf_report.xlsx
@@ -84,7 +84,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>205</t>
+    <t>206</t>
   </si>
   <si>
     <t>4위</t>
@@ -141,7 +141,7 @@
     <t>Lv.9</t>
   </si>
   <si>
-    <t>2644조 5010억 8910만</t>
+    <t>2660조 412억 4594만</t>
   </si>
   <si>
     <t>초코남</t>
@@ -156,7 +156,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>360</t>
+    <t>362</t>
   </si>
   <si>
     <t>10위</t>
@@ -180,7 +180,7 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>352</t>
+    <t>355</t>
   </si>
   <si>
     <t>28위</t>
@@ -189,7 +189,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>1782조 8658억 6921만</t>
+    <t>1783조 6767억 9537만</t>
   </si>
   <si>
     <t>비련길드 모집조건 : 투력 10조 이상 일일기부 300+ 길컨 참여자</t>
@@ -207,7 +207,7 @@
     <t>Scania 33</t>
   </si>
   <si>
-    <t>598</t>
+    <t>599</t>
   </si>
   <si>
     <t>7위</t>
@@ -231,13 +231,13 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%80%ED%81%AC%EB%9F%B0</t>
   </si>
   <si>
-    <t>892</t>
+    <t>891</t>
   </si>
   <si>
     <t>70위</t>
   </si>
   <si>
-    <t>269조 9519억 1727만</t>
+    <t>270조 534억 597만</t>
   </si>
   <si>
     <t>1일 미접 강퇴합니다 업그레이드 꾸준히 해주세요 길갑문의 : 정뽀</t>
@@ -1005,7 +1005,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%8F%84%EC%A0%81%EB%8F%84%EC%95%84</t>
   </si>
   <si>
-    <t>108조 6452억 9023만</t>
+    <t>109조 4906억 272만</t>
   </si>
   <si>
     <t>썬콜법사도희</t>
@@ -1014,7 +1014,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9C%EB%B2%95%EC%82%AC%EB%8F%84%ED%9D%AC</t>
   </si>
   <si>
-    <t>79조 391억 1692만</t>
+    <t>80조 7045억 9195만</t>
   </si>
   <si>
     <t>유랑민</t>
@@ -1044,6 +1044,15 @@
     <t>64조 4958억 7415만</t>
   </si>
   <si>
+    <t>연바기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>50조 9293억 2547만</t>
+  </si>
+  <si>
     <t>봇대</t>
   </si>
   <si>
@@ -1065,15 +1074,6 @@
     <t>48조 2467억 7400만</t>
   </si>
   <si>
-    <t>연바기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%B0%EB%B0%94%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>47조 3259억 5536만</t>
-  </si>
-  <si>
     <t>limno</t>
   </si>
   <si>
@@ -1116,7 +1116,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%B9%98%EC%95%B5</t>
   </si>
   <si>
-    <t>35조 2947억 8635만</t>
+    <t>35조 7902억 9732만</t>
   </si>
   <si>
     <t>불곰파워</t>
@@ -1125,7 +1125,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EA%B3%B0%ED%8C%8C%EC%9B%8C</t>
   </si>
   <si>
-    <t>33조 6373억 4379만</t>
+    <t>34조 5145억 3848만</t>
   </si>
   <si>
     <t>히어로경원</t>
@@ -1170,7 +1170,16 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A7%80%EC%A1%B4%EC%8D%AC%EC%BD%9Clz</t>
   </si>
   <si>
-    <t>28조 2458억 8022만</t>
+    <t>28조 3266억 7278만</t>
+  </si>
+  <si>
+    <t>구파발고양이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>25조 9625억 2100만</t>
   </si>
   <si>
     <t>A7R4</t>
@@ -1179,7 +1188,7 @@
     <t>https://mgf.gg/contents/character.php?n=A7R4</t>
   </si>
   <si>
-    <t>25조 2127억 5854만</t>
+    <t>25조 5738억 6580만</t>
   </si>
   <si>
     <t>낮잠중</t>
@@ -1197,7 +1206,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%BF%A0%EB%AF%B8</t>
   </si>
   <si>
-    <t>22조 9706억 3096만</t>
+    <t>23조 8703억 7100만</t>
   </si>
   <si>
     <t>썹웨피망빼</t>
@@ -1209,15 +1218,6 @@
     <t>19조 3237억 9663만</t>
   </si>
   <si>
-    <t>구파발고양이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%ED%8C%8C%EB%B0%9C%EA%B3%A0%EC%96%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>18조 4055억 5481만</t>
-  </si>
-  <si>
     <t>극쪽이</t>
   </si>
   <si>
@@ -1632,7 +1632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%AF%B8l</t>
   </si>
   <si>
-    <t>4조 1408억 7254만</t>
+    <t>4조 1415억 8223만</t>
   </si>
   <si>
     <t>야로야옹</t>
@@ -1944,7 +1944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EA%B5%AC%EB%BF%8C%EC%85%94</t>
   </si>
   <si>
-    <t>12조 1490억 5330만</t>
+    <t>12조 1592억 6415만</t>
   </si>
   <si>
     <t>훈다띠</t>
@@ -1962,7 +1962,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%88%AC%EB%83%89</t>
   </si>
   <si>
-    <t>3조 3432억 7208만</t>
+    <t>3조 3794억 3309만</t>
   </si>
   <si>
     <t>알뺘노</t>
@@ -2010,7 +2010,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>787억 9614만</t>
+    <t>788억 7515만</t>
   </si>
   <si>
     <t>문싸</t>
@@ -2022,7 +2022,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>602억 3212만</t>
+    <t>628억 6329만</t>
   </si>
   <si>
     <t>신기리불주먹</t>
@@ -2037,7 +2037,7 @@
     <t>86</t>
   </si>
   <si>
-    <t>196억 6968만</t>
+    <t>203억 7092만</t>
   </si>
   <si>
     <t>DoomFist</t>
@@ -5241,13 +5241,13 @@
         <v>82</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>339</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>162</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>23</v>
@@ -5261,22 +5261,22 @@
         <v>135</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>116</v>
+        <v>162</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>343</v>
@@ -5305,10 +5305,10 @@
         <v>82</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>346</v>
@@ -5340,7 +5340,7 @@
         <v>115</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>162</v>
+        <v>116</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>349</v>
@@ -5689,10 +5689,10 @@
         <v>82</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>181</v>
+        <v>162</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>382</v>
@@ -5724,7 +5724,7 @@
         <v>125</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>385</v>
@@ -5753,7 +5753,7 @@
         <v>82</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>190</v>
@@ -5785,10 +5785,10 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>207</v>
+        <v>95</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>391</v>
@@ -5817,7 +5817,7 @@
         <v>82</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>105</v>
+        <v>207</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>181</v>
@@ -6221,7 +6221,7 @@
         <v>82</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>116</v>
@@ -6829,7 +6829,7 @@
         <v>82</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>190</v>
@@ -7105,7 +7105,7 @@
         <v>82</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>116</v>
